--- a/Table1_Supplementary.xlsx
+++ b/Table1_Supplementary.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2DDE4DD-88F3-4474-9A48-4EE05F6FC1AA}"/>
+  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F28FEBD3-5C94-47EF-B78A-65F9C7870413}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>cmebl</t>
   </si>
   <si>
-    <t>ldex</t>
-  </si>
-  <si>
     <t>cate</t>
   </si>
   <si>
@@ -85,6 +82,9 @@
   </si>
   <si>
     <t>Blast against UniProt</t>
+  </si>
+  <si>
+    <t>dehII</t>
   </si>
 </sst>
 </file>
@@ -467,11 +467,11 @@
     <row r="1" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="6"/>
       <c r="D1" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1"/>
     </row>
@@ -484,10 +484,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
@@ -495,16 +495,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>16</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>17</v>
       </c>
       <c r="D3" s="2">
         <v>0</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
@@ -534,8 +534,8 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A6" s="2" t="s">
-        <v>6</v>
+      <c r="A6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>4</v>
@@ -548,36 +548,36 @@
     </row>
     <row r="7" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="C7" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D7" s="4">
         <v>5</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>10</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="D8" s="2">
         <v>0</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/Table1_Supplementary.xlsx
+++ b/Table1_Supplementary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F28FEBD3-5C94-47EF-B78A-65F9C7870413}"/>
+  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CDEE0F9-424B-45EE-B916-526607CFC4E9}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -91,7 +91,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -115,6 +115,14 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -152,10 +160,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -175,8 +184,12 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -190,6 +203,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -503,7 +520,7 @@
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="7" t="s">
         <v>12</v>
       </c>
     </row>
@@ -585,6 +602,9 @@
     <mergeCell ref="B1:C1"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="E3" r:id="rId1" xr:uid="{731F6750-FF84-4E45-B7C4-024C38A41F78}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Table1_Supplementary.xlsx
+++ b/Table1_Supplementary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipiit-my.sharepoint.com/personal/g_semeraro1_studenti_unipi_it/Documents/UniPi/Tesi/THESIS/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="110" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CDEE0F9-424B-45EE-B916-526607CFC4E9}"/>
+  <xr:revisionPtr revIDLastSave="111" documentId="11_AD4D5CB4E552A5DACE1C6445E8DA5B2E5ADEDD88" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{72A83398-DC35-4033-8911-F35F79BC2247}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="19396" windowHeight="11475" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="21">
   <si>
     <t>F</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>dehII</t>
+  </si>
+  <si>
+    <t xml:space="preserve">studiati e testati esclusivamente su sphing quindi è out of scope dal mio obiettivo. </t>
   </si>
 </sst>
 </file>
@@ -164,7 +167,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -181,10 +184,13 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -203,10 +209,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -472,7 +474,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr defaultRowHeight="14.35" customHeight="1" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="2" max="2" width="25.265625" customWidth="1"/>
@@ -481,18 +483,18 @@
     <col min="5" max="5" width="39.3984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C1" s="6"/>
+      <c r="C1" s="7"/>
       <c r="D1" s="5" t="s">
         <v>18</v>
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A2" s="1"/>
       <c r="B2" s="5" t="s">
         <v>0</v>
@@ -507,7 +509,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A3" s="2" t="s">
         <v>2</v>
       </c>
@@ -520,11 +522,14 @@
       <c r="D3" s="2">
         <v>0</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="6" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="F3" s="8" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -537,7 +542,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="3"/>
     </row>
-    <row r="5" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
@@ -550,7 +555,7 @@
       <c r="D5" s="2"/>
       <c r="E5" s="2"/>
     </row>
-    <row r="6" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
@@ -563,7 +568,7 @@
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
-    <row r="7" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
@@ -580,7 +585,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:6" ht="14.35" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
